--- a/output/differences_relative_local.xlsx
+++ b/output/differences_relative_local.xlsx
@@ -399,7 +399,7 @@
         <v>4.138067017238316</v>
       </c>
       <c r="D2">
-        <v>6.101812692441322</v>
+        <v>7.244278125404903</v>
       </c>
       <c r="E2" s="2">
         <v>41395</v>
@@ -416,7 +416,7 @@
         <v>-10.04410364329197</v>
       </c>
       <c r="D3">
-        <v>0.2985074626865661</v>
+        <v>5.197244834063864</v>
       </c>
       <c r="E3" s="2">
         <v>41426</v>
@@ -433,7 +433,7 @@
         <v>-8.095720084297925</v>
       </c>
       <c r="D4">
-        <v>9.257424938700613</v>
+        <v>10.4010825846709</v>
       </c>
       <c r="E4" s="2">
         <v>41456</v>
@@ -450,7 +450,7 @@
         <v>-7.312398662947206</v>
       </c>
       <c r="D5">
-        <v>2.773490016431817</v>
+        <v>2.167550462777967</v>
       </c>
       <c r="E5" s="2">
         <v>41487</v>
@@ -467,7 +467,7 @@
         <v>-5.885241895125457</v>
       </c>
       <c r="D6">
-        <v>-5.00510725229825</v>
+        <v>-9.268292682926834</v>
       </c>
       <c r="E6" s="2">
         <v>41518</v>
@@ -484,7 +484,7 @@
         <v>-6.136501809008934</v>
       </c>
       <c r="D7">
-        <v>-12.66009321049038</v>
+        <v>-11.71964910408743</v>
       </c>
       <c r="E7" s="2">
         <v>41760</v>
@@ -501,7 +501,7 @@
         <v>-13.07916635602827</v>
       </c>
       <c r="D8">
-        <v>2.686567164179111</v>
+        <v>7.701941139636821</v>
       </c>
       <c r="E8" s="2">
         <v>41791</v>
@@ -518,7 +518,7 @@
         <v>-9.202851066669147</v>
       </c>
       <c r="D9">
-        <v>-5.473913255281489</v>
+        <v>-4.484456640228543</v>
       </c>
       <c r="E9" s="2">
         <v>41821</v>
@@ -535,7 +535,7 @@
         <v>3.29803452706039</v>
       </c>
       <c r="D10">
-        <v>-3.201712891500261</v>
+        <v>-3.772423401337028</v>
       </c>
       <c r="E10" s="2">
         <v>41852</v>
@@ -552,7 +552,7 @@
         <v>1.281766994722552</v>
       </c>
       <c r="D11">
-        <v>-3.983656792645547</v>
+        <v>-8.292682926829277</v>
       </c>
       <c r="E11" s="2">
         <v>41883</v>
@@ -569,7 +569,7 @@
         <v>-6.62829555252918</v>
       </c>
       <c r="D12">
-        <v>-5.220027076569162</v>
+        <v>-4.199471064805963</v>
       </c>
       <c r="E12" s="2">
         <v>42125</v>
@@ -586,7 +586,7 @@
         <v>-19.210073806925</v>
       </c>
       <c r="D13">
-        <v>-14.82587064676618</v>
+        <v>-10.66583176789816</v>
       </c>
       <c r="E13" s="2">
         <v>42156</v>
@@ -603,7 +603,7 @@
         <v>-13.50626641219419</v>
       </c>
       <c r="D14">
-        <v>-21.43286296542878</v>
+        <v>-20.61045746720295</v>
       </c>
       <c r="E14" s="2">
         <v>42186</v>
@@ -620,7 +620,7 @@
         <v>-3.799710208311531</v>
       </c>
       <c r="D15">
-        <v>17.3529851117861</v>
+        <v>16.66108669121856</v>
       </c>
       <c r="E15" s="2">
         <v>42217</v>
@@ -637,7 +637,7 @@
         <v>7.591966356834938</v>
       </c>
       <c r="D16">
-        <v>11.84882533197142</v>
+        <v>6.82926829268292</v>
       </c>
       <c r="E16" s="2">
         <v>42248</v>
@@ -654,7 +654,7 @@
         <v>3.709516987303121</v>
       </c>
       <c r="D17">
-        <v>7.395737237471089</v>
+        <v>8.552135175714714</v>
       </c>
       <c r="E17" s="2">
         <v>42491</v>
@@ -671,7 +671,7 @@
         <v>-2.802186923346326</v>
       </c>
       <c r="D18">
-        <v>19.40298507462686</v>
+        <v>25.23481527864745</v>
       </c>
       <c r="E18" s="2">
         <v>42522</v>
@@ -688,7 +688,7 @@
         <v>0.2984374650100058</v>
       </c>
       <c r="D19">
-        <v>-22.04666872351136</v>
+        <v>-21.23068826824043</v>
       </c>
       <c r="E19" s="2">
         <v>42552</v>
@@ -705,7 +705,7 @@
         <v>-16.11393193216824</v>
       </c>
       <c r="D20">
-        <v>-9.17691579943236</v>
+        <v>-9.712397265452042</v>
       </c>
       <c r="E20" s="2">
         <v>42583</v>
@@ -722,7 +722,7 @@
         <v>-20.0664926867856</v>
       </c>
       <c r="D21">
-        <v>-23.77425944841674</v>
+        <v>-27.19512195121952</v>
       </c>
       <c r="E21" s="2">
         <v>42614</v>
@@ -739,7 +739,7 @@
         <v>-9.447015609782303</v>
       </c>
       <c r="D22">
-        <v>-1.230426396060712</v>
+        <v>-0.1669118263507118</v>
       </c>
       <c r="E22" s="2">
         <v>42856</v>
@@ -756,7 +756,7 @@
         <v>-9.05953243149853</v>
       </c>
       <c r="D23">
-        <v>-15.42288557213931</v>
+        <v>-11.29200584429139</v>
       </c>
       <c r="E23" s="2">
         <v>42887</v>
@@ -773,7 +773,7 @@
         <v>-5.630101598684497</v>
       </c>
       <c r="D24">
-        <v>-11.61197083610737</v>
+        <v>-10.68676465060332</v>
       </c>
       <c r="E24" s="2">
         <v>42917</v>
@@ -790,7 +790,7 @@
         <v>-2.589709476998664</v>
       </c>
       <c r="D25">
-        <v>-1.767664193596586</v>
+        <v>-2.346829673949452</v>
       </c>
       <c r="E25" s="2">
         <v>42948</v>
@@ -807,7 +807,7 @@
         <v>-6.476192204175829</v>
       </c>
       <c r="D26">
-        <v>-34.37180796731359</v>
+        <v>-37.31707317073171</v>
       </c>
       <c r="E26" s="2">
         <v>42979</v>
